--- a/data/trans_bre/CAGE_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/CAGE_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; -0,05</t>
+          <t>-1,37; 0,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; -1,03</t>
+          <t>-3,0; -1,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; -1,13</t>
+          <t>-3,35; -1,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -1,54</t>
+          <t>-8,42; -1,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 47,52</t>
+          <t>-100,0; 87,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -54,42</t>
+          <t>-100,0; -55,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -5,47</t>
+          <t>-100,0; 0,08</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,09; -0,09</t>
+          <t>-1,1; -0,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,63; -1,17</t>
+          <t>-2,58; -1,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,59; -0,41</t>
+          <t>-1,58; -0,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,5</t>
+          <t>-1,41; 1,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,93; 27,43</t>
+          <t>-93,51; -7,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,1; -62,36</t>
+          <t>-95,04; -63,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-84,97; -29,95</t>
+          <t>-86,94; -26,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,59; 148,69</t>
+          <t>-75,68; 163,63</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,78</t>
+          <t>-1,15; 0,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,4</t>
+          <t>-3,21; -0,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,88</t>
+          <t>-0,77; 1,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,83</t>
+          <t>-3,23; 0,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-80,83; 883,69</t>
+          <t>-100,0; 944,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-85,82; 71,58</t>
+          <t>-87,78; 51,42</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,92; -0,18</t>
+          <t>-0,86; -0,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,35; -1,32</t>
+          <t>-2,34; -1,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,5; -0,5</t>
+          <t>-1,52; -0,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,31</t>
+          <t>-2,17; 0,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,85; -26,54</t>
+          <t>-86,05; -20,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-97,3; -81,65</t>
+          <t>-97,26; -82,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-82,92; -41,2</t>
+          <t>-82,11; -37,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,03; 17,48</t>
+          <t>-75,48; 10,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/CAGE_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/CAGE_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,63</t>
+          <t>-4,62</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-78,5%</t>
+          <t>-79,59%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,04</t>
+          <t>-1,42; -0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; -1,08</t>
+          <t>-3,04; -1,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; -1,06</t>
+          <t>-3,54; -1,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; -1,3</t>
+          <t>-8,08; -1,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 87,2</t>
+          <t>-100,0; 62,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -55,9</t>
+          <t>-100,0; -64,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,08</t>
+          <t>-100,0; -22,65</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,1; -0,1</t>
+          <t>-1,05; -0,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,58; -1,22</t>
+          <t>-2,6; -1,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,58; -0,38</t>
+          <t>-1,54; -0,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,47</t>
+          <t>-0,82; 2,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-93,51; -7,52</t>
+          <t>-92,83; 2,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,04; -63,92</t>
+          <t>-95,08; -68,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-86,94; -26,43</t>
+          <t>-85,33; -28,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,68; 163,63</t>
+          <t>-47,6; 261,31</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>-1,41</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-43,83%</t>
+          <t>-47,21%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,85</t>
+          <t>-1,11; 0,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,34</t>
+          <t>-3,23; -0,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,83</t>
+          <t>-0,85; 1,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,6</t>
+          <t>-3,58; 0,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 944,54</t>
+          <t>-79,01; 942,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-87,78; 51,42</t>
+          <t>-85,33; 50,31</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-41,45%</t>
+          <t>-24,74%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,86; -0,18</t>
+          <t>-0,88; -0,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,34; -1,32</t>
+          <t>-2,34; -1,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,52; -0,47</t>
+          <t>-1,45; -0,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,19</t>
+          <t>-1,78; 0,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,05; -20,23</t>
+          <t>-84,41; -11,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-97,26; -82,99</t>
+          <t>-97,2; -80,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-82,11; -37,54</t>
+          <t>-80,29; -35,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,48; 10,28</t>
+          <t>-57,94; 34,24</t>
         </is>
       </c>
     </row>
